--- a/docs/Test_Report/Gpt/TestPlanExecutionReport_Gpt.xlsx
+++ b/docs/Test_Report/Gpt/TestPlanExecutionReport_Gpt.xlsx
@@ -43,7 +43,7 @@
       <sz val="16"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -77,6 +77,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="000000FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
@@ -99,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -131,10 +136,13 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -716,7 +724,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629,MCAL-29630</t>
+          <t>MCAL-30757,MCAL-30813</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -726,7 +734,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2025-03-14 01:57:44.149343-05:00 CDT</t>
+          <t>2025-06-09 07:28:57.401207-05:00 CDT</t>
         </is>
       </c>
     </row>
@@ -798,12 +806,12 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>67</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -835,12 +843,12 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -872,12 +880,12 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1020,12 +1028,12 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>84</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -1111,12 +1119,12 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>17%</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -1143,12 +1151,12 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>17%</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -1175,12 +1183,12 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1556,12 +1564,12 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -1668,12 +1676,12 @@
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S2" s="3" t="inlineStr"/>
@@ -1687,12 +1695,12 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -1799,12 +1807,12 @@
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr"/>
@@ -1818,12 +1826,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1930,12 +1938,12 @@
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr"/>
@@ -1949,12 +1957,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -2061,12 +2069,12 @@
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr"/>
@@ -2080,12 +2088,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -2192,12 +2200,12 @@
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr"/>
@@ -2211,12 +2219,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -2323,12 +2331,12 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr"/>
@@ -2342,12 +2350,12 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -2454,12 +2462,12 @@
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr"/>
@@ -2473,12 +2481,12 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -2585,12 +2593,12 @@
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr"/>
@@ -2604,12 +2612,12 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -2716,12 +2724,12 @@
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr"/>
@@ -2735,12 +2743,12 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -2847,12 +2855,12 @@
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr"/>
@@ -2866,12 +2874,12 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -2978,12 +2986,12 @@
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr"/>
@@ -2997,12 +3005,12 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -3109,12 +3117,12 @@
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr"/>
@@ -3128,12 +3136,12 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -3240,12 +3248,12 @@
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr"/>
@@ -3259,12 +3267,12 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -3371,12 +3379,12 @@
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr"/>
@@ -3390,12 +3398,12 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -3502,12 +3510,12 @@
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr"/>
@@ -3521,12 +3529,12 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -3633,12 +3641,12 @@
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr"/>
@@ -3652,12 +3660,12 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -3764,12 +3772,12 @@
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr"/>
@@ -3783,12 +3791,12 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -3895,12 +3903,12 @@
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr"/>
@@ -3914,12 +3922,12 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -4026,12 +4034,12 @@
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr"/>
@@ -4045,12 +4053,12 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -4157,12 +4165,12 @@
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr"/>
@@ -4176,12 +4184,12 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -4288,12 +4296,12 @@
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr"/>
@@ -4307,12 +4315,12 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -4419,12 +4427,12 @@
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr"/>
@@ -4438,12 +4446,12 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -4550,12 +4558,12 @@
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr"/>
@@ -4569,12 +4577,12 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -4681,12 +4689,12 @@
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr"/>
@@ -4700,12 +4708,12 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -4720,12 +4728,12 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Design,Design,Design</t>
+          <t>Design,Design</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28451,MCAL-22017,MCAL-22018</t>
+          <t>MCAL-22017,MCAL-22018</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -4812,12 +4820,12 @@
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr"/>
@@ -4831,12 +4839,12 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -4943,12 +4951,12 @@
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr"/>
@@ -4962,12 +4970,12 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -5074,12 +5082,12 @@
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr"/>
@@ -5093,12 +5101,12 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -5205,12 +5213,12 @@
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr"/>
@@ -5224,12 +5232,12 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -5336,12 +5344,12 @@
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr"/>
@@ -5355,12 +5363,12 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -5467,12 +5475,12 @@
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr"/>
@@ -5486,12 +5494,12 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -5598,12 +5606,12 @@
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr"/>
@@ -5617,12 +5625,12 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -5729,12 +5737,12 @@
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr"/>
@@ -5748,12 +5756,12 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -5860,12 +5868,12 @@
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr"/>
@@ -5879,12 +5887,12 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -5991,12 +5999,12 @@
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr"/>
@@ -6010,12 +6018,12 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -6122,12 +6130,12 @@
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr"/>
@@ -6141,12 +6149,12 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -6253,12 +6261,12 @@
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr"/>
@@ -6272,12 +6280,12 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -6384,12 +6392,12 @@
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr"/>
@@ -6403,12 +6411,12 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -6515,12 +6523,12 @@
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr"/>
@@ -6534,12 +6542,12 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -6646,12 +6654,12 @@
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr"/>
@@ -6665,12 +6673,12 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -6777,12 +6785,12 @@
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr"/>
@@ -6796,12 +6804,12 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -6908,12 +6916,12 @@
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr"/>
@@ -6927,12 +6935,12 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -7039,12 +7047,12 @@
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr"/>
@@ -7058,12 +7066,12 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -7170,12 +7178,12 @@
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr"/>
@@ -7189,12 +7197,12 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -7301,12 +7309,12 @@
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr"/>
@@ -7320,12 +7328,12 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -7432,12 +7440,12 @@
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr"/>
@@ -7451,12 +7459,12 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -7563,12 +7571,12 @@
       </c>
       <c r="Q47" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R47" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S47" s="3" t="inlineStr"/>
@@ -7582,12 +7590,12 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -7694,12 +7702,12 @@
       </c>
       <c r="Q48" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R48" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S48" s="3" t="inlineStr"/>
@@ -7713,12 +7721,12 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -7825,12 +7833,12 @@
       </c>
       <c r="Q49" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R49" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S49" s="3" t="inlineStr"/>
@@ -7844,12 +7852,12 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -7956,12 +7964,12 @@
       </c>
       <c r="Q50" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R50" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S50" s="3" t="inlineStr"/>
@@ -7975,12 +7983,12 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -8087,12 +8095,12 @@
       </c>
       <c r="Q51" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R51" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S51" s="3" t="inlineStr"/>
@@ -8106,12 +8114,12 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -8218,12 +8226,12 @@
       </c>
       <c r="Q52" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R52" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S52" s="3" t="inlineStr"/>
@@ -8237,12 +8245,12 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -8349,12 +8357,12 @@
       </c>
       <c r="Q53" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R53" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S53" s="3" t="inlineStr"/>
@@ -8368,12 +8376,12 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -8480,12 +8488,12 @@
       </c>
       <c r="Q54" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R54" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S54" s="3" t="inlineStr"/>
@@ -8499,12 +8507,12 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -8611,12 +8619,12 @@
       </c>
       <c r="Q55" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R55" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S55" s="3" t="inlineStr"/>
@@ -8630,12 +8638,12 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -8742,12 +8750,12 @@
       </c>
       <c r="Q56" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R56" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S56" s="3" t="inlineStr"/>
@@ -8761,12 +8769,12 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -8873,12 +8881,12 @@
       </c>
       <c r="Q57" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R57" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S57" s="3" t="inlineStr"/>
@@ -8892,12 +8900,12 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -9004,12 +9012,12 @@
       </c>
       <c r="Q58" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R58" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S58" s="3" t="inlineStr"/>
@@ -9023,12 +9031,12 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -9135,12 +9143,12 @@
       </c>
       <c r="Q59" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R59" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S59" s="3" t="inlineStr"/>
@@ -9154,12 +9162,12 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -9266,12 +9274,12 @@
       </c>
       <c r="Q60" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R60" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S60" s="3" t="inlineStr"/>
@@ -9285,12 +9293,12 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -9397,12 +9405,12 @@
       </c>
       <c r="Q61" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R61" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S61" s="3" t="inlineStr"/>
@@ -9416,12 +9424,12 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -9528,12 +9536,12 @@
       </c>
       <c r="Q62" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R62" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S62" s="3" t="inlineStr"/>
@@ -9547,12 +9555,12 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -9659,12 +9667,12 @@
       </c>
       <c r="Q63" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R63" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S63" s="3" t="inlineStr"/>
@@ -9678,12 +9686,12 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -9790,12 +9798,12 @@
       </c>
       <c r="Q64" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R64" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S64" s="3" t="inlineStr"/>
@@ -9809,12 +9817,12 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -9921,12 +9929,12 @@
       </c>
       <c r="Q65" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R65" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S65" s="3" t="inlineStr"/>
@@ -9940,12 +9948,12 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -10052,12 +10060,12 @@
       </c>
       <c r="Q66" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R66" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S66" s="3" t="inlineStr"/>
@@ -10071,12 +10079,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -10183,12 +10191,12 @@
       </c>
       <c r="Q67" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R67" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S67" s="3" t="inlineStr"/>
@@ -10202,12 +10210,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -10314,12 +10322,12 @@
       </c>
       <c r="Q68" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R68" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S68" s="3" t="inlineStr"/>
@@ -10333,12 +10341,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -10445,12 +10453,12 @@
       </c>
       <c r="Q69" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R69" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S69" s="3" t="inlineStr"/>
@@ -10464,12 +10472,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -10576,12 +10584,12 @@
       </c>
       <c r="Q70" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R70" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S70" s="3" t="inlineStr"/>
@@ -10595,12 +10603,12 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -10707,12 +10715,12 @@
       </c>
       <c r="Q71" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R71" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S71" s="3" t="inlineStr"/>
@@ -10726,12 +10734,12 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -10838,12 +10846,12 @@
       </c>
       <c r="Q72" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R72" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S72" s="3" t="inlineStr"/>
@@ -10857,12 +10865,12 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -10969,12 +10977,12 @@
       </c>
       <c r="Q73" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R73" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S73" s="3" t="inlineStr"/>
@@ -10988,12 +10996,12 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -11100,12 +11108,12 @@
       </c>
       <c r="Q74" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R74" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S74" s="3" t="inlineStr"/>
@@ -11119,12 +11127,12 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -11231,12 +11239,12 @@
       </c>
       <c r="Q75" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R75" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S75" s="3" t="inlineStr"/>
@@ -11250,12 +11258,12 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -11362,12 +11370,12 @@
       </c>
       <c r="Q76" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R76" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S76" s="3" t="inlineStr"/>
@@ -11381,12 +11389,12 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -11493,12 +11501,12 @@
       </c>
       <c r="Q77" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R77" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S77" s="3" t="inlineStr"/>
@@ -11512,12 +11520,12 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -11624,12 +11632,12 @@
       </c>
       <c r="Q78" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R78" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S78" s="3" t="inlineStr"/>
@@ -11643,12 +11651,12 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -11755,12 +11763,12 @@
       </c>
       <c r="Q79" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R79" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S79" s="3" t="inlineStr"/>
@@ -11774,12 +11782,12 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -11886,12 +11894,12 @@
       </c>
       <c r="Q80" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R80" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S80" s="3" t="inlineStr"/>
@@ -11905,12 +11913,12 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -12017,12 +12025,12 @@
       </c>
       <c r="Q81" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R81" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S81" s="3" t="inlineStr"/>
@@ -12036,12 +12044,12 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -12148,12 +12156,12 @@
       </c>
       <c r="Q82" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R82" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S82" s="3" t="inlineStr"/>
@@ -12167,12 +12175,12 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -12279,12 +12287,12 @@
       </c>
       <c r="Q83" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R83" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S83" s="3" t="inlineStr"/>
@@ -12298,12 +12306,12 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -12410,12 +12418,12 @@
       </c>
       <c r="Q84" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R84" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S84" s="3" t="inlineStr"/>
@@ -12429,12 +12437,12 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29627</t>
+          <t>MCAL-30763</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
@@ -12541,12 +12549,12 @@
       </c>
       <c r="Q85" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29629</t>
+          <t>MCAL-30757</t>
         </is>
       </c>
       <c r="R85" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S85" s="3" t="inlineStr"/>
@@ -12560,12 +12568,12 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29628</t>
+          <t>MCAL-30814</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -12580,12 +12588,12 @@
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Design,Design</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28452</t>
+          <t>MCAL-28452,MCAL-22029</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
@@ -12672,31 +12680,31 @@
       </c>
       <c r="Q86" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29630</t>
+          <t>MCAL-30813</t>
         </is>
       </c>
       <c r="R86" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
         </is>
       </c>
       <c r="S86" s="3" t="inlineStr"/>
       <c r="T86" s="3" t="inlineStr"/>
-      <c r="U86" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U86" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29628</t>
+          <t>MCAL-30814</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -12711,12 +12719,12 @@
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Design,Design</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>MCAL-21998</t>
+          <t>MCAL-21998,MCAL-21992</t>
         </is>
       </c>
       <c r="G87" s="3" t="inlineStr">
@@ -12803,31 +12811,31 @@
       </c>
       <c r="Q87" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29630</t>
+          <t>MCAL-30813</t>
         </is>
       </c>
       <c r="R87" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
         </is>
       </c>
       <c r="S87" s="3" t="inlineStr"/>
       <c r="T87" s="3" t="inlineStr"/>
-      <c r="U87" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U87" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29628</t>
+          <t>MCAL-30814</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -12840,8 +12848,16 @@
           <t>Negative test case to validate the Gpt_InitPriv() API when DET error check is off and invalid SimMode is given</t>
         </is>
       </c>
-      <c r="E88" s="3" t="inlineStr"/>
-      <c r="F88" s="3" t="inlineStr"/>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-22029</t>
+        </is>
+      </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm,F29P58x-evm</t>
@@ -12926,31 +12942,31 @@
       </c>
       <c r="Q88" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29630</t>
+          <t>MCAL-30813</t>
         </is>
       </c>
       <c r="R88" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
         </is>
       </c>
       <c r="S88" s="3" t="inlineStr"/>
       <c r="T88" s="3" t="inlineStr"/>
-      <c r="U88" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U88" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29628</t>
+          <t>MCAL-30814</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -12963,8 +12979,16 @@
           <t>Positive test case to validate the Gpt_EnableNotification() and Gpt_DisableNotification() APIs when DET error check is off</t>
         </is>
       </c>
-      <c r="E89" s="3" t="inlineStr"/>
-      <c r="F89" s="3" t="inlineStr"/>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-22029</t>
+        </is>
+      </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm,F29P58x-evm</t>
@@ -13049,31 +13073,31 @@
       </c>
       <c r="Q89" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29630</t>
+          <t>MCAL-30813</t>
         </is>
       </c>
       <c r="R89" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
         </is>
       </c>
       <c r="S89" s="3" t="inlineStr"/>
       <c r="T89" s="3" t="inlineStr"/>
-      <c r="U89" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U89" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29628</t>
+          <t>MCAL-30814</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
@@ -13148,31 +13172,31 @@
       </c>
       <c r="Q90" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29630</t>
+          <t>MCAL-30813</t>
         </is>
       </c>
       <c r="R90" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
         </is>
       </c>
       <c r="S90" s="3" t="inlineStr"/>
       <c r="T90" s="3" t="inlineStr"/>
-      <c r="U90" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U90" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29628</t>
+          <t>MCAL-30814</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -13192,7 +13216,7 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>MCAL-12327,MCAL-12305,MCAL-25467,MCAL-12412,MCAL-12411,MCAL-12410,MCAL-12389,MCAL-12374,MCAL-12355,MCAL-12309,MCAL-12448,MCAL-12395,MCAL-12379,MCAL-12375,MCAL-12446,MCAL-25460,MCAL-25458,MCAL-12345,MCAL-12341,MCAL-12356,MCAL-12338,MCAL-12335,MCAL-12333,MCAL-12332,MCAL-12427,MCAL-12421,MCAL-12418,MCAL-25456,MCAL-12376,MCAL-12340,MCAL-12316,MCAL-12312,MCAL-12310,MCAL-12361,MCAL-12399,MCAL-12326,MCAL-25455,MCAL-25471,MCAL-25469,MCAL-25461,MCAL-12337,MCAL-12334,MCAL-12323,MCAL-12303,MCAL-12425,MCAL-12447,MCAL-12438,MCAL-12444,MCAL-12357,MCAL-12330</t>
+          <t>MCAL-12327,MCAL-12305,MCAL-25467,MCAL-12412,MCAL-12411,MCAL-12410,MCAL-12389,MCAL-12374,MCAL-12355,MCAL-12309,MCAL-12448,MCAL-12395,MCAL-12379,MCAL-12375,MCAL-12446,MCAL-25460,MCAL-25458,MCAL-12345,MCAL-12341,MCAL-12445,MCAL-12356,MCAL-12338,MCAL-12335,MCAL-12333,MCAL-12332,MCAL-12366,MCAL-12306,MCAL-12360,MCAL-12396,MCAL-12427,MCAL-12421,MCAL-12418,MCAL-25456,MCAL-12376,MCAL-12340,MCAL-12316,MCAL-12312,MCAL-12310,MCAL-12361,MCAL-12399,MCAL-12326,MCAL-25455,MCAL-25471,MCAL-25469,MCAL-25461,MCAL-12337,MCAL-12334,MCAL-12323,MCAL-12303,MCAL-12425</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
@@ -13247,31 +13271,31 @@
       </c>
       <c r="Q91" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29630</t>
+          <t>MCAL-30813</t>
         </is>
       </c>
       <c r="R91" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
         </is>
       </c>
       <c r="S91" s="3" t="inlineStr"/>
       <c r="T91" s="3" t="inlineStr"/>
-      <c r="U91" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U91" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29628</t>
+          <t>MCAL-30814</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
@@ -13346,31 +13370,31 @@
       </c>
       <c r="Q92" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29630</t>
+          <t>MCAL-30813</t>
         </is>
       </c>
       <c r="R92" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
         </is>
       </c>
       <c r="S92" s="3" t="inlineStr"/>
       <c r="T92" s="3" t="inlineStr"/>
-      <c r="U92" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U92" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29628</t>
+          <t>MCAL-30814</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -13445,31 +13469,31 @@
       </c>
       <c r="Q93" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29630</t>
+          <t>MCAL-30813</t>
         </is>
       </c>
       <c r="R93" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
         </is>
       </c>
       <c r="S93" s="3" t="inlineStr"/>
       <c r="T93" s="3" t="inlineStr"/>
-      <c r="U93" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U93" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29628</t>
+          <t>MCAL-30814</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -13544,31 +13568,31 @@
       </c>
       <c r="Q94" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29630</t>
+          <t>MCAL-30813</t>
         </is>
       </c>
       <c r="R94" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
         </is>
       </c>
       <c r="S94" s="3" t="inlineStr"/>
       <c r="T94" s="3" t="inlineStr"/>
-      <c r="U94" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U94" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29628</t>
+          <t>MCAL-30814</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -13643,31 +13667,31 @@
       </c>
       <c r="Q95" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29630</t>
+          <t>MCAL-30813</t>
         </is>
       </c>
       <c r="R95" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
         </is>
       </c>
       <c r="S95" s="3" t="inlineStr"/>
       <c r="T95" s="3" t="inlineStr"/>
-      <c r="U95" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U95" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29628</t>
+          <t>MCAL-30814</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
@@ -13742,31 +13766,31 @@
       </c>
       <c r="Q96" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29630</t>
+          <t>MCAL-30813</t>
         </is>
       </c>
       <c r="R96" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
         </is>
       </c>
       <c r="S96" s="3" t="inlineStr"/>
       <c r="T96" s="3" t="inlineStr"/>
-      <c r="U96" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U96" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29628</t>
+          <t>MCAL-30814</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
@@ -13779,8 +13803,16 @@
           <t>GPT driver code build: GptWakeupFunctionalityApi  : On</t>
         </is>
       </c>
-      <c r="E97" s="3" t="inlineStr"/>
-      <c r="F97" s="3" t="inlineStr"/>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-22029</t>
+        </is>
+      </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm,F29P58x-evm</t>
@@ -13833,31 +13865,31 @@
       </c>
       <c r="Q97" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29630</t>
+          <t>MCAL-30813</t>
         </is>
       </c>
       <c r="R97" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
         </is>
       </c>
       <c r="S97" s="3" t="inlineStr"/>
       <c r="T97" s="3" t="inlineStr"/>
-      <c r="U97" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U97" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29628</t>
+          <t>MCAL-30814</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
@@ -13932,31 +13964,31 @@
       </c>
       <c r="Q98" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29630</t>
+          <t>MCAL-30813</t>
         </is>
       </c>
       <c r="R98" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
         </is>
       </c>
       <c r="S98" s="3" t="inlineStr"/>
       <c r="T98" s="3" t="inlineStr"/>
-      <c r="U98" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U98" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29628</t>
+          <t>MCAL-30814</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
@@ -14031,31 +14063,31 @@
       </c>
       <c r="Q99" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29630</t>
+          <t>MCAL-30813</t>
         </is>
       </c>
       <c r="R99" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
         </is>
       </c>
       <c r="S99" s="3" t="inlineStr"/>
       <c r="T99" s="3" t="inlineStr"/>
-      <c r="U99" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U99" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29628</t>
+          <t>MCAL-30814</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
@@ -14130,31 +14162,31 @@
       </c>
       <c r="Q100" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29630</t>
+          <t>MCAL-30813</t>
         </is>
       </c>
       <c r="R100" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
         </is>
       </c>
       <c r="S100" s="3" t="inlineStr"/>
       <c r="T100" s="3" t="inlineStr"/>
-      <c r="U100" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U100" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29628</t>
+          <t>MCAL-30814</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
@@ -14229,31 +14261,31 @@
       </c>
       <c r="Q101" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29630</t>
+          <t>MCAL-30813</t>
         </is>
       </c>
       <c r="R101" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
         </is>
       </c>
       <c r="S101" s="3" t="inlineStr"/>
       <c r="T101" s="3" t="inlineStr"/>
-      <c r="U101" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U101" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29628</t>
+          <t>MCAL-30814</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
@@ -14328,31 +14360,31 @@
       </c>
       <c r="Q102" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29630</t>
+          <t>MCAL-30813</t>
         </is>
       </c>
       <c r="R102" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
         </is>
       </c>
       <c r="S102" s="3" t="inlineStr"/>
       <c r="T102" s="3" t="inlineStr"/>
-      <c r="U102" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U102" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29628</t>
+          <t>MCAL-30814</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
@@ -14427,31 +14459,31 @@
       </c>
       <c r="Q103" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29630</t>
+          <t>MCAL-30813</t>
         </is>
       </c>
       <c r="R103" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
         </is>
       </c>
       <c r="S103" s="3" t="inlineStr"/>
       <c r="T103" s="3" t="inlineStr"/>
-      <c r="U103" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U103" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29628</t>
+          <t>MCAL-30814</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
@@ -14526,31 +14558,31 @@
       </c>
       <c r="Q104" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29630</t>
+          <t>MCAL-30813</t>
         </is>
       </c>
       <c r="R104" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
         </is>
       </c>
       <c r="S104" s="3" t="inlineStr"/>
       <c r="T104" s="3" t="inlineStr"/>
-      <c r="U104" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U104" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29628</t>
+          <t>MCAL-30814</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
@@ -14625,31 +14657,31 @@
       </c>
       <c r="Q105" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29630</t>
+          <t>MCAL-30813</t>
         </is>
       </c>
       <c r="R105" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
         </is>
       </c>
       <c r="S105" s="3" t="inlineStr"/>
       <c r="T105" s="3" t="inlineStr"/>
-      <c r="U105" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U105" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29628</t>
+          <t>MCAL-30814</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
@@ -14724,31 +14756,31 @@
       </c>
       <c r="Q106" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29630</t>
+          <t>MCAL-30813</t>
         </is>
       </c>
       <c r="R106" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
         </is>
       </c>
       <c r="S106" s="3" t="inlineStr"/>
       <c r="T106" s="3" t="inlineStr"/>
-      <c r="U106" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U106" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29628</t>
+          <t>MCAL-30814</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
@@ -14823,31 +14855,31 @@
       </c>
       <c r="Q107" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29630</t>
+          <t>MCAL-30813</t>
         </is>
       </c>
       <c r="R107" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
         </is>
       </c>
       <c r="S107" s="3" t="inlineStr"/>
       <c r="T107" s="3" t="inlineStr"/>
-      <c r="U107" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U107" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29628</t>
+          <t>MCAL-30814</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
@@ -14922,31 +14954,31 @@
       </c>
       <c r="Q108" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29630</t>
+          <t>MCAL-30813</t>
         </is>
       </c>
       <c r="R108" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
         </is>
       </c>
       <c r="S108" s="3" t="inlineStr"/>
       <c r="T108" s="3" t="inlineStr"/>
-      <c r="U108" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U108" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29628</t>
+          <t>MCAL-30814</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
@@ -15021,31 +15053,31 @@
       </c>
       <c r="Q109" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29630</t>
+          <t>MCAL-30813</t>
         </is>
       </c>
       <c r="R109" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
         </is>
       </c>
       <c r="S109" s="3" t="inlineStr"/>
       <c r="T109" s="3" t="inlineStr"/>
-      <c r="U109" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U109" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29628</t>
+          <t>MCAL-30814</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
@@ -15120,31 +15152,31 @@
       </c>
       <c r="Q110" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29630</t>
+          <t>MCAL-30813</t>
         </is>
       </c>
       <c r="R110" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
         </is>
       </c>
       <c r="S110" s="3" t="inlineStr"/>
       <c r="T110" s="3" t="inlineStr"/>
-      <c r="U110" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U110" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29628</t>
+          <t>MCAL-30814</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
@@ -15219,31 +15251,31 @@
       </c>
       <c r="Q111" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29630</t>
+          <t>MCAL-30813</t>
         </is>
       </c>
       <c r="R111" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
         </is>
       </c>
       <c r="S111" s="3" t="inlineStr"/>
       <c r="T111" s="3" t="inlineStr"/>
-      <c r="U111" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U111" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29628</t>
+          <t>MCAL-30814</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
@@ -15318,31 +15350,31 @@
       </c>
       <c r="Q112" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29630</t>
+          <t>MCAL-30813</t>
         </is>
       </c>
       <c r="R112" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
         </is>
       </c>
       <c r="S112" s="3" t="inlineStr"/>
       <c r="T112" s="3" t="inlineStr"/>
-      <c r="U112" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U112" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29628</t>
+          <t>MCAL-30814</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
@@ -15417,31 +15449,31 @@
       </c>
       <c r="Q113" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29630</t>
+          <t>MCAL-30813</t>
         </is>
       </c>
       <c r="R113" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
         </is>
       </c>
       <c r="S113" s="3" t="inlineStr"/>
       <c r="T113" s="3" t="inlineStr"/>
-      <c r="U113" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U113" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29628</t>
+          <t>MCAL-30814</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
@@ -15516,19 +15548,19 @@
       </c>
       <c r="Q114" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29630</t>
+          <t>MCAL-30813</t>
         </is>
       </c>
       <c r="R114" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
         </is>
       </c>
       <c r="S114" s="3" t="inlineStr"/>
       <c r="T114" s="3" t="inlineStr"/>
-      <c r="U114" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U114" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
@@ -15582,12 +15614,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>Test Plan</t>
         </is>
       </c>
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>Test Plan Key</t>
         </is>
@@ -15609,8 +15641,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="n"/>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="A3" s="12" t="n"/>
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Test Plan Name</t>
         </is>
@@ -15632,8 +15664,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="n"/>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="A4" s="12" t="n"/>
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>Test Case Key</t>
         </is>
@@ -15655,8 +15687,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="n"/>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="A5" s="12" t="n"/>
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Test Case Name</t>
         </is>
@@ -15678,8 +15710,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="n"/>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="A6" s="12" t="n"/>
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>Associated Issue(s) Type</t>
         </is>
@@ -15706,8 +15738,8 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="n"/>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="A7" s="12" t="n"/>
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>Associated Issue(s) ID(s)</t>
         </is>
@@ -15729,8 +15761,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="n"/>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="A8" s="12" t="n"/>
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>Test Platform</t>
         </is>
@@ -15752,8 +15784,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="n"/>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="A9" s="12" t="n"/>
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>Test Level</t>
         </is>
@@ -15769,7 +15801,7 @@
 -- "Not Provided" if no 'Test Scope' is provided in Jira</t>
         </is>
       </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -15781,8 +15813,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="n"/>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="A10" s="12" t="n"/>
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>Test Description</t>
         </is>
@@ -15804,8 +15836,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="n"/>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="A11" s="12" t="n"/>
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>Test Setup</t>
         </is>
@@ -15827,8 +15859,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="n"/>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="A12" s="12" t="n"/>
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>Pass/Fail Criteria</t>
         </is>
@@ -15850,8 +15882,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="n"/>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="A13" s="12" t="n"/>
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>Test Type</t>
         </is>
@@ -15862,7 +15894,7 @@
 (Map Test Method from Qmetry)</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -15874,15 +15906,15 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="n"/>
-      <c r="B14" s="12" t="n"/>
+      <c r="A14" s="12" t="n"/>
+      <c r="B14" s="13" t="n"/>
       <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Functional:
 Tests covering functional requirements-based  aspects of the software</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -15894,8 +15926,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="n"/>
-      <c r="B15" s="12" t="n"/>
+      <c r="A15" s="12" t="n"/>
+      <c r="B15" s="13" t="n"/>
       <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Compatability:
@@ -15903,7 +15935,7 @@
 ISO/IEC/IEEE 29119-1 Defn: type of testing that measures the degree to which a test item can function satisfactorily alongside other independent products in a shared environment (co-existence), and where necessary, exchanges information with other systems or components (interoperability)</t>
         </is>
       </c>
-      <c r="D15" s="11" t="inlineStr">
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -15915,15 +15947,15 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="n"/>
-      <c r="B16" s="12" t="n"/>
+      <c r="A16" s="12" t="n"/>
+      <c r="B16" s="13" t="n"/>
       <c r="C16" s="3" t="inlineStr">
         <is>
           <t>Usability:
 Test Case covers usability/api/look and feel aspects of the module including out-of box (OOB) experience</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -15935,15 +15967,15 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="n"/>
-      <c r="B17" s="12" t="n"/>
+      <c r="A17" s="12" t="n"/>
+      <c r="B17" s="13" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Fault Injection:
 Testing based on injection of errors or faults to ensure no unintended consequences</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D17" s="12" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -15955,8 +15987,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="n"/>
-      <c r="B18" s="12" t="n"/>
+      <c r="A18" s="12" t="n"/>
+      <c r="B18" s="13" t="n"/>
       <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Performance: 
@@ -15964,7 +15996,7 @@
 ISO/IEC/IEEE 29119-1 Defn: type of testing conducted to evaluate the degree to which a test item accomplishes its designated functions within given constraints of time and other resources</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -15976,8 +16008,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="n"/>
-      <c r="B19" s="12" t="n"/>
+      <c r="A19" s="12" t="n"/>
+      <c r="B19" s="13" t="n"/>
       <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Reliability: 
@@ -15985,7 +16017,7 @@
 ISO/IEC/IEEE 29119-1 Defn: type of testing conducted to evaluate the ability of a test item to perform its required functions, including evaluating the frequency with which failures occur, when it is used under stated conditions for a specified period of time</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D19" s="12" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -15997,8 +16029,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="n"/>
-      <c r="B20" s="12" t="n"/>
+      <c r="A20" s="12" t="n"/>
+      <c r="B20" s="13" t="n"/>
       <c r="C20" s="3" t="inlineStr">
         <is>
           <t>Stress:
@@ -16006,7 +16038,7 @@
 ISO/IEC/IEEE 29119-1 Defn: type of performance efficiency testing conducted to evaluate a test item's behaviour under conditions of loading above anticipated or specified capacity requirements, or of resource availability below minimum specified requirements</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="D20" s="12" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -16018,8 +16050,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="n"/>
-      <c r="B21" s="12" t="n"/>
+      <c r="A21" s="12" t="n"/>
+      <c r="B21" s="13" t="n"/>
       <c r="C21" s="3" t="inlineStr">
         <is>
           <t>Security:
@@ -16027,7 +16059,7 @@
 ISO/IEC/IEEE 29119-1 Defn: type of testing conducted to evaluate the degree to which a test item, and associated data and information, are protected so that unauthorized persons or systems cannot use, read, or modify them, and authorized persons or systems are not denied access to them</t>
         </is>
       </c>
-      <c r="D21" s="11" t="inlineStr">
+      <c r="D21" s="12" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -16039,8 +16071,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="n"/>
-      <c r="B22" s="12" t="n"/>
+      <c r="A22" s="12" t="n"/>
+      <c r="B22" s="13" t="n"/>
       <c r="C22" s="3" t="inlineStr">
         <is>
           <t>Maintainability:
@@ -16048,7 +16080,7 @@
 ISO/IEC/IEEE 29119-1 Defn: test type conducted to evaluate the degree of effectiveness and efficiency with which a test item may be modified</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="D22" s="12" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -16060,8 +16092,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="n"/>
-      <c r="B23" s="12" t="n"/>
+      <c r="A23" s="12" t="n"/>
+      <c r="B23" s="13" t="n"/>
       <c r="C23" s="3" t="inlineStr">
         <is>
           <t>Portability:
@@ -16069,7 +16101,7 @@
 ISO/IEC/IEEE 29119-1 Defn: type of testing conducted to evaluate the ease with which a test item can be transferred from one hardware or software environment to another, including the level of modification needed for it to be executed in various types of environment</t>
         </is>
       </c>
-      <c r="D23" s="11" t="inlineStr">
+      <c r="D23" s="12" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -16081,8 +16113,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="n"/>
-      <c r="B24" s="12" t="inlineStr">
+      <c r="A24" s="12" t="n"/>
+      <c r="B24" s="13" t="inlineStr">
         <is>
           <t>Test Design Technique</t>
         </is>
@@ -16094,7 +16126,7 @@
 (Map Test Derivation Method from Qmetry)</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="D24" s="12" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -16106,8 +16138,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="n"/>
-      <c r="B25" s="12" t="n"/>
+      <c r="A25" s="12" t="n"/>
+      <c r="B25" s="13" t="n"/>
       <c r="C25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Requirements-Analysis:
@@ -16115,7 +16147,7 @@
 </t>
         </is>
       </c>
-      <c r="D25" s="11" t="inlineStr">
+      <c r="D25" s="12" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -16127,15 +16159,15 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="n"/>
-      <c r="B26" s="12" t="n"/>
+      <c r="A26" s="12" t="n"/>
+      <c r="B26" s="13" t="n"/>
       <c r="C26" s="3" t="inlineStr">
         <is>
           <t>Boundary Value Analysis:
 Test cases that apply to interfaces and values approaching and crossing the boundaries and out of range values</t>
         </is>
       </c>
-      <c r="D26" s="11" t="inlineStr">
+      <c r="D26" s="12" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -16147,15 +16179,15 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="n"/>
-      <c r="B27" s="12" t="n"/>
+      <c r="A27" s="12" t="n"/>
+      <c r="B27" s="13" t="n"/>
       <c r="C27" s="3" t="inlineStr">
         <is>
           <t>Error Guessing:
 Test cases established based on lessons learned and expert judgement to determine situations that may cause software failures or errors to appear</t>
         </is>
       </c>
-      <c r="D27" s="11" t="inlineStr">
+      <c r="D27" s="12" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -16167,28 +16199,28 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="n"/>
-      <c r="B28" s="12" t="n"/>
+      <c r="A28" s="12" t="n"/>
+      <c r="B28" s="13" t="n"/>
       <c r="C28" s="3" t="inlineStr">
         <is>
           <t>Other (Use case analysis; Customer Usage; Requirement analysis; Failure Mode analysis):
 Teams are encouraged to use techniques defined by standards such as ISO/IEC/IEEE 29119-4; which needs to be refelcted within Qmetry</t>
         </is>
       </c>
-      <c r="D28" s="11" t="inlineStr">
+      <c r="D28" s="12" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="E28" s="11" t="inlineStr">
+      <c r="E28" s="12" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="n"/>
-      <c r="B29" s="12" t="inlineStr">
+      <c r="A29" s="12" t="n"/>
+      <c r="B29" s="13" t="inlineStr">
         <is>
           <t>Test Execution Type</t>
         </is>
@@ -16198,7 +16230,7 @@
           <t>Identifies whether the case is automated or manually or Semi-Automated executed</t>
         </is>
       </c>
-      <c r="D29" s="11" t="inlineStr">
+      <c r="D29" s="12" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -16210,8 +16242,8 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="n"/>
-      <c r="B30" s="12" t="inlineStr">
+      <c r="A30" s="12" t="n"/>
+      <c r="B30" s="13" t="inlineStr">
         <is>
           <t>Test Category</t>
         </is>
@@ -16221,7 +16253,7 @@
           <t>Test Categories represent sets of tests that are commonly used.</t>
         </is>
       </c>
-      <c r="D30" s="11" t="inlineStr">
+      <c r="D30" s="12" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -16233,15 +16265,15 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="n"/>
-      <c r="B31" s="12" t="n"/>
+      <c r="A31" s="12" t="n"/>
+      <c r="B31" s="13" t="n"/>
       <c r="C31" s="3" t="inlineStr">
         <is>
           <t>Sanity:
 This Test case is identified to run for Sanity Checks. These are mainly the basic tests that need to be run as part of entry to validate phase</t>
         </is>
       </c>
-      <c r="D31" s="11" t="inlineStr">
+      <c r="D31" s="12" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -16253,15 +16285,15 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="n"/>
-      <c r="B32" s="12" t="n"/>
+      <c r="A32" s="12" t="n"/>
+      <c r="B32" s="13" t="n"/>
       <c r="C32" s="3" t="inlineStr">
         <is>
           <t>Full:
 This category means running all test cases for identified releases</t>
         </is>
       </c>
-      <c r="D32" s="11" t="inlineStr">
+      <c r="D32" s="12" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -16273,15 +16305,15 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="n"/>
-      <c r="B33" s="12" t="n"/>
+      <c r="A33" s="12" t="n"/>
+      <c r="B33" s="13" t="n"/>
       <c r="C33" s="3" t="inlineStr">
         <is>
           <t>Base Regression:
 This Test case is identified to run for the Base Regression / maintenance releases</t>
         </is>
       </c>
-      <c r="D33" s="11" t="inlineStr">
+      <c r="D33" s="12" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -16293,8 +16325,8 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="11" t="n"/>
-      <c r="B34" s="12" t="inlineStr">
+      <c r="A34" s="12" t="n"/>
+      <c r="B34" s="13" t="inlineStr">
         <is>
           <t>Test Component(s)</t>
         </is>
@@ -16304,24 +16336,24 @@
           <t xml:space="preserve">The field provides the Component(s) (in Jira) to which the Test Case is mapped to. </t>
         </is>
       </c>
-      <c r="D34" s="11" t="inlineStr">
+      <c r="D34" s="12" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="E34" s="11" t="inlineStr">
+      <c r="E34" s="12" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="13" t="inlineStr">
+      <c r="A35" s="14" t="inlineStr">
         <is>
           <t>Test Execution</t>
         </is>
       </c>
-      <c r="B35" s="12" t="inlineStr">
+      <c r="B35" s="13" t="inlineStr">
         <is>
           <t>Build/Release Key</t>
         </is>
@@ -16343,8 +16375,8 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="13" t="n"/>
-      <c r="B36" s="12" t="inlineStr">
+      <c r="A36" s="14" t="n"/>
+      <c r="B36" s="13" t="inlineStr">
         <is>
           <t>Defect Key</t>
         </is>
@@ -16366,8 +16398,8 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="13" t="n"/>
-      <c r="B37" s="12" t="inlineStr">
+      <c r="A37" s="14" t="n"/>
+      <c r="B37" s="13" t="inlineStr">
         <is>
           <t>Defect Summary</t>
         </is>
@@ -16389,8 +16421,8 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="13" t="n"/>
-      <c r="B38" s="12" t="inlineStr">
+      <c r="A38" s="14" t="n"/>
+      <c r="B38" s="13" t="inlineStr">
         <is>
           <t>Overall Status</t>
         </is>
@@ -16413,8 +16445,8 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="13" t="n"/>
-      <c r="B39" s="12" t="n"/>
+      <c r="A39" s="14" t="n"/>
+      <c r="B39" s="13" t="n"/>
       <c r="C39" s="3" t="inlineStr">
         <is>
           <t>PASS
@@ -16433,8 +16465,8 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="13" t="n"/>
-      <c r="B40" s="12" t="n"/>
+      <c r="A40" s="14" t="n"/>
+      <c r="B40" s="13" t="n"/>
       <c r="C40" s="3" t="inlineStr">
         <is>
           <t>FAIL
@@ -16453,8 +16485,8 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="13" t="n"/>
-      <c r="B41" s="12" t="n"/>
+      <c r="A41" s="14" t="n"/>
+      <c r="B41" s="13" t="n"/>
       <c r="C41" s="3" t="inlineStr">
         <is>
           <t>BLOCKED
@@ -16473,8 +16505,8 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="13" t="n"/>
-      <c r="B42" s="12" t="n"/>
+      <c r="A42" s="14" t="n"/>
+      <c r="B42" s="13" t="n"/>
       <c r="C42" s="3" t="inlineStr">
         <is>
           <t>WIP

--- a/docs/Test_Report/Gpt/TestPlanExecutionReport_Gpt.xlsx
+++ b/docs/Test_Report/Gpt/TestPlanExecutionReport_Gpt.xlsx
@@ -43,7 +43,7 @@
       <sz val="16"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -77,11 +77,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000000FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
@@ -104,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -136,13 +131,10 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -724,7 +716,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757,MCAL-30813</t>
+          <t>MCAL-32354,MCAL-32351</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -734,7 +726,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2025-06-09 07:28:57.401207-05:00 CDT</t>
+          <t>2025-08-29 04:53:09.680216-05:00 CDT</t>
         </is>
       </c>
     </row>
@@ -806,12 +798,12 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>81</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -843,12 +835,12 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -880,12 +872,12 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1028,12 +1020,12 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>113</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -1119,12 +1111,12 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -1151,12 +1143,12 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -1183,12 +1175,12 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1564,12 +1556,12 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -1676,12 +1668,12 @@
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S2" s="3" t="inlineStr"/>
@@ -1695,12 +1687,12 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -1807,12 +1799,12 @@
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr"/>
@@ -1826,12 +1818,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1938,12 +1930,12 @@
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr"/>
@@ -1957,12 +1949,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -2069,12 +2061,12 @@
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr"/>
@@ -2088,12 +2080,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -2200,12 +2192,12 @@
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr"/>
@@ -2219,12 +2211,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -2331,12 +2323,12 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr"/>
@@ -2350,12 +2342,12 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -2462,12 +2454,12 @@
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr"/>
@@ -2481,12 +2473,12 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -2593,12 +2585,12 @@
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr"/>
@@ -2612,12 +2604,12 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -2724,12 +2716,12 @@
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr"/>
@@ -2743,12 +2735,12 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -2855,12 +2847,12 @@
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr"/>
@@ -2874,12 +2866,12 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -2986,12 +2978,12 @@
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr"/>
@@ -3005,12 +2997,12 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -3117,12 +3109,12 @@
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr"/>
@@ -3136,12 +3128,12 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -3248,12 +3240,12 @@
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr"/>
@@ -3267,12 +3259,12 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -3379,12 +3371,12 @@
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr"/>
@@ -3398,12 +3390,12 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -3510,12 +3502,12 @@
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr"/>
@@ -3529,12 +3521,12 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -3641,12 +3633,12 @@
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr"/>
@@ -3660,12 +3652,12 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -3772,12 +3764,12 @@
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr"/>
@@ -3791,12 +3783,12 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -3903,12 +3895,12 @@
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr"/>
@@ -3922,12 +3914,12 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -4034,12 +4026,12 @@
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr"/>
@@ -4053,12 +4045,12 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -4165,12 +4157,12 @@
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr"/>
@@ -4184,12 +4176,12 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -4296,12 +4288,12 @@
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr"/>
@@ -4315,12 +4307,12 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -4427,12 +4419,12 @@
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr"/>
@@ -4446,12 +4438,12 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -4558,12 +4550,12 @@
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr"/>
@@ -4577,12 +4569,12 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -4689,12 +4681,12 @@
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr"/>
@@ -4708,12 +4700,12 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -4820,12 +4812,12 @@
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr"/>
@@ -4839,12 +4831,12 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -4951,12 +4943,12 @@
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr"/>
@@ -4970,12 +4962,12 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -5082,12 +5074,12 @@
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr"/>
@@ -5101,12 +5093,12 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -5213,12 +5205,12 @@
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr"/>
@@ -5232,12 +5224,12 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -5344,12 +5336,12 @@
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr"/>
@@ -5363,12 +5355,12 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -5475,12 +5467,12 @@
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr"/>
@@ -5494,12 +5486,12 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -5606,12 +5598,12 @@
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr"/>
@@ -5625,12 +5617,12 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -5737,12 +5729,12 @@
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr"/>
@@ -5756,12 +5748,12 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -5868,12 +5860,12 @@
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr"/>
@@ -5887,12 +5879,12 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -5999,12 +5991,12 @@
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr"/>
@@ -6018,12 +6010,12 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -6130,12 +6122,12 @@
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr"/>
@@ -6149,12 +6141,12 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -6261,12 +6253,12 @@
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr"/>
@@ -6280,12 +6272,12 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -6392,12 +6384,12 @@
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr"/>
@@ -6411,12 +6403,12 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -6523,12 +6515,12 @@
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr"/>
@@ -6542,12 +6534,12 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -6654,12 +6646,12 @@
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr"/>
@@ -6673,12 +6665,12 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -6785,12 +6777,12 @@
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr"/>
@@ -6804,12 +6796,12 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -6916,12 +6908,12 @@
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr"/>
@@ -6935,12 +6927,12 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -7047,12 +7039,12 @@
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr"/>
@@ -7066,12 +7058,12 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -7178,12 +7170,12 @@
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr"/>
@@ -7197,12 +7189,12 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -7309,12 +7301,12 @@
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr"/>
@@ -7328,12 +7320,12 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -7440,12 +7432,12 @@
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr"/>
@@ -7459,12 +7451,12 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -7571,12 +7563,12 @@
       </c>
       <c r="Q47" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R47" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S47" s="3" t="inlineStr"/>
@@ -7590,12 +7582,12 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -7702,12 +7694,12 @@
       </c>
       <c r="Q48" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R48" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S48" s="3" t="inlineStr"/>
@@ -7721,12 +7713,12 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -7833,12 +7825,12 @@
       </c>
       <c r="Q49" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R49" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S49" s="3" t="inlineStr"/>
@@ -7852,12 +7844,12 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -7964,12 +7956,12 @@
       </c>
       <c r="Q50" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R50" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S50" s="3" t="inlineStr"/>
@@ -7983,12 +7975,12 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -8095,12 +8087,12 @@
       </c>
       <c r="Q51" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R51" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S51" s="3" t="inlineStr"/>
@@ -8114,12 +8106,12 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -8226,12 +8218,12 @@
       </c>
       <c r="Q52" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R52" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S52" s="3" t="inlineStr"/>
@@ -8245,12 +8237,12 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -8357,12 +8349,12 @@
       </c>
       <c r="Q53" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R53" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S53" s="3" t="inlineStr"/>
@@ -8376,12 +8368,12 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -8488,12 +8480,12 @@
       </c>
       <c r="Q54" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R54" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S54" s="3" t="inlineStr"/>
@@ -8507,12 +8499,12 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -8619,12 +8611,12 @@
       </c>
       <c r="Q55" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R55" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S55" s="3" t="inlineStr"/>
@@ -8638,12 +8630,12 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -8750,12 +8742,12 @@
       </c>
       <c r="Q56" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R56" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S56" s="3" t="inlineStr"/>
@@ -8769,12 +8761,12 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -8881,12 +8873,12 @@
       </c>
       <c r="Q57" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R57" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S57" s="3" t="inlineStr"/>
@@ -8900,12 +8892,12 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -9012,12 +9004,12 @@
       </c>
       <c r="Q58" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R58" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S58" s="3" t="inlineStr"/>
@@ -9031,12 +9023,12 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -9143,12 +9135,12 @@
       </c>
       <c r="Q59" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R59" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S59" s="3" t="inlineStr"/>
@@ -9162,12 +9154,12 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -9274,12 +9266,12 @@
       </c>
       <c r="Q60" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R60" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S60" s="3" t="inlineStr"/>
@@ -9293,12 +9285,12 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -9405,12 +9397,12 @@
       </c>
       <c r="Q61" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R61" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S61" s="3" t="inlineStr"/>
@@ -9424,12 +9416,12 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -9536,12 +9528,12 @@
       </c>
       <c r="Q62" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R62" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S62" s="3" t="inlineStr"/>
@@ -9555,12 +9547,12 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -9667,12 +9659,12 @@
       </c>
       <c r="Q63" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R63" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S63" s="3" t="inlineStr"/>
@@ -9686,12 +9678,12 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -9798,12 +9790,12 @@
       </c>
       <c r="Q64" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R64" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S64" s="3" t="inlineStr"/>
@@ -9817,12 +9809,12 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -9929,12 +9921,12 @@
       </c>
       <c r="Q65" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R65" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S65" s="3" t="inlineStr"/>
@@ -9948,12 +9940,12 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -10060,12 +10052,12 @@
       </c>
       <c r="Q66" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R66" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S66" s="3" t="inlineStr"/>
@@ -10079,12 +10071,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -10191,12 +10183,12 @@
       </c>
       <c r="Q67" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R67" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S67" s="3" t="inlineStr"/>
@@ -10210,12 +10202,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -10322,12 +10314,12 @@
       </c>
       <c r="Q68" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R68" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S68" s="3" t="inlineStr"/>
@@ -10341,12 +10333,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -10453,12 +10445,12 @@
       </c>
       <c r="Q69" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R69" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S69" s="3" t="inlineStr"/>
@@ -10472,12 +10464,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -10584,12 +10576,12 @@
       </c>
       <c r="Q70" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R70" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S70" s="3" t="inlineStr"/>
@@ -10603,12 +10595,12 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -10715,12 +10707,12 @@
       </c>
       <c r="Q71" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R71" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S71" s="3" t="inlineStr"/>
@@ -10734,12 +10726,12 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -10846,12 +10838,12 @@
       </c>
       <c r="Q72" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R72" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S72" s="3" t="inlineStr"/>
@@ -10865,12 +10857,12 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -10977,12 +10969,12 @@
       </c>
       <c r="Q73" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R73" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S73" s="3" t="inlineStr"/>
@@ -10996,12 +10988,12 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -11108,12 +11100,12 @@
       </c>
       <c r="Q74" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R74" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S74" s="3" t="inlineStr"/>
@@ -11127,12 +11119,12 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -11239,12 +11231,12 @@
       </c>
       <c r="Q75" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R75" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S75" s="3" t="inlineStr"/>
@@ -11258,12 +11250,12 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -11370,12 +11362,12 @@
       </c>
       <c r="Q76" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R76" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S76" s="3" t="inlineStr"/>
@@ -11389,12 +11381,12 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -11501,12 +11493,12 @@
       </c>
       <c r="Q77" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R77" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S77" s="3" t="inlineStr"/>
@@ -11520,12 +11512,12 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -11632,12 +11624,12 @@
       </c>
       <c r="Q78" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R78" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S78" s="3" t="inlineStr"/>
@@ -11651,12 +11643,12 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -11763,12 +11755,12 @@
       </c>
       <c r="Q79" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R79" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S79" s="3" t="inlineStr"/>
@@ -11782,12 +11774,12 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -11894,12 +11886,12 @@
       </c>
       <c r="Q80" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R80" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S80" s="3" t="inlineStr"/>
@@ -11913,12 +11905,12 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -12025,12 +12017,12 @@
       </c>
       <c r="Q81" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R81" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S81" s="3" t="inlineStr"/>
@@ -12044,12 +12036,12 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -12156,12 +12148,12 @@
       </c>
       <c r="Q82" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R82" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S82" s="3" t="inlineStr"/>
@@ -12175,12 +12167,12 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -12287,12 +12279,12 @@
       </c>
       <c r="Q83" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R83" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S83" s="3" t="inlineStr"/>
@@ -12306,12 +12298,12 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -12418,12 +12410,12 @@
       </c>
       <c r="Q84" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R84" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S84" s="3" t="inlineStr"/>
@@ -12437,12 +12429,12 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30763</t>
+          <t>MCAL-32355</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
@@ -12549,12 +12541,12 @@
       </c>
       <c r="Q85" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30757</t>
+          <t>MCAL-32354</t>
         </is>
       </c>
       <c r="R85" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Automated Tests Run</t>
         </is>
       </c>
       <c r="S85" s="3" t="inlineStr"/>
@@ -12568,12 +12560,12 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30814</t>
+          <t>MCAL-32352</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -12680,31 +12672,31 @@
       </c>
       <c r="Q86" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30813</t>
+          <t>MCAL-32351</t>
         </is>
       </c>
       <c r="R86" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Test Run</t>
         </is>
       </c>
       <c r="S86" s="3" t="inlineStr"/>
       <c r="T86" s="3" t="inlineStr"/>
-      <c r="U86" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U86" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30814</t>
+          <t>MCAL-32352</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -12811,31 +12803,31 @@
       </c>
       <c r="Q87" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30813</t>
+          <t>MCAL-32351</t>
         </is>
       </c>
       <c r="R87" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Test Run</t>
         </is>
       </c>
       <c r="S87" s="3" t="inlineStr"/>
       <c r="T87" s="3" t="inlineStr"/>
-      <c r="U87" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U87" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30814</t>
+          <t>MCAL-32352</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -12942,31 +12934,31 @@
       </c>
       <c r="Q88" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30813</t>
+          <t>MCAL-32351</t>
         </is>
       </c>
       <c r="R88" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Test Run</t>
         </is>
       </c>
       <c r="S88" s="3" t="inlineStr"/>
       <c r="T88" s="3" t="inlineStr"/>
-      <c r="U88" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U88" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30814</t>
+          <t>MCAL-32352</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -13073,31 +13065,31 @@
       </c>
       <c r="Q89" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30813</t>
+          <t>MCAL-32351</t>
         </is>
       </c>
       <c r="R89" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Test Run</t>
         </is>
       </c>
       <c r="S89" s="3" t="inlineStr"/>
       <c r="T89" s="3" t="inlineStr"/>
-      <c r="U89" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U89" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30814</t>
+          <t>MCAL-32352</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
@@ -13172,31 +13164,31 @@
       </c>
       <c r="Q90" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30813</t>
+          <t>MCAL-32351</t>
         </is>
       </c>
       <c r="R90" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Test Run</t>
         </is>
       </c>
       <c r="S90" s="3" t="inlineStr"/>
       <c r="T90" s="3" t="inlineStr"/>
-      <c r="U90" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U90" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30814</t>
+          <t>MCAL-32352</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -13271,31 +13263,31 @@
       </c>
       <c r="Q91" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30813</t>
+          <t>MCAL-32351</t>
         </is>
       </c>
       <c r="R91" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Test Run</t>
         </is>
       </c>
       <c r="S91" s="3" t="inlineStr"/>
       <c r="T91" s="3" t="inlineStr"/>
-      <c r="U91" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U91" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30814</t>
+          <t>MCAL-32352</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
@@ -13370,31 +13362,31 @@
       </c>
       <c r="Q92" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30813</t>
+          <t>MCAL-32351</t>
         </is>
       </c>
       <c r="R92" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Test Run</t>
         </is>
       </c>
       <c r="S92" s="3" t="inlineStr"/>
       <c r="T92" s="3" t="inlineStr"/>
-      <c r="U92" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U92" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30814</t>
+          <t>MCAL-32352</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -13469,31 +13461,31 @@
       </c>
       <c r="Q93" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30813</t>
+          <t>MCAL-32351</t>
         </is>
       </c>
       <c r="R93" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Test Run</t>
         </is>
       </c>
       <c r="S93" s="3" t="inlineStr"/>
       <c r="T93" s="3" t="inlineStr"/>
-      <c r="U93" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U93" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30814</t>
+          <t>MCAL-32352</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -13568,31 +13560,31 @@
       </c>
       <c r="Q94" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30813</t>
+          <t>MCAL-32351</t>
         </is>
       </c>
       <c r="R94" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Test Run</t>
         </is>
       </c>
       <c r="S94" s="3" t="inlineStr"/>
       <c r="T94" s="3" t="inlineStr"/>
-      <c r="U94" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U94" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30814</t>
+          <t>MCAL-32352</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -13667,31 +13659,31 @@
       </c>
       <c r="Q95" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30813</t>
+          <t>MCAL-32351</t>
         </is>
       </c>
       <c r="R95" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Test Run</t>
         </is>
       </c>
       <c r="S95" s="3" t="inlineStr"/>
       <c r="T95" s="3" t="inlineStr"/>
-      <c r="U95" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U95" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30814</t>
+          <t>MCAL-32352</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
@@ -13766,31 +13758,31 @@
       </c>
       <c r="Q96" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30813</t>
+          <t>MCAL-32351</t>
         </is>
       </c>
       <c r="R96" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Test Run</t>
         </is>
       </c>
       <c r="S96" s="3" t="inlineStr"/>
       <c r="T96" s="3" t="inlineStr"/>
-      <c r="U96" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U96" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30814</t>
+          <t>MCAL-32352</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
@@ -13865,31 +13857,31 @@
       </c>
       <c r="Q97" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30813</t>
+          <t>MCAL-32351</t>
         </is>
       </c>
       <c r="R97" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Test Run</t>
         </is>
       </c>
       <c r="S97" s="3" t="inlineStr"/>
       <c r="T97" s="3" t="inlineStr"/>
-      <c r="U97" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U97" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30814</t>
+          <t>MCAL-32352</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
@@ -13964,31 +13956,31 @@
       </c>
       <c r="Q98" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30813</t>
+          <t>MCAL-32351</t>
         </is>
       </c>
       <c r="R98" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Test Run</t>
         </is>
       </c>
       <c r="S98" s="3" t="inlineStr"/>
       <c r="T98" s="3" t="inlineStr"/>
-      <c r="U98" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U98" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30814</t>
+          <t>MCAL-32352</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
@@ -14063,31 +14055,31 @@
       </c>
       <c r="Q99" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30813</t>
+          <t>MCAL-32351</t>
         </is>
       </c>
       <c r="R99" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Test Run</t>
         </is>
       </c>
       <c r="S99" s="3" t="inlineStr"/>
       <c r="T99" s="3" t="inlineStr"/>
-      <c r="U99" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U99" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30814</t>
+          <t>MCAL-32352</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
@@ -14162,31 +14154,31 @@
       </c>
       <c r="Q100" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30813</t>
+          <t>MCAL-32351</t>
         </is>
       </c>
       <c r="R100" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Test Run</t>
         </is>
       </c>
       <c r="S100" s="3" t="inlineStr"/>
       <c r="T100" s="3" t="inlineStr"/>
-      <c r="U100" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U100" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30814</t>
+          <t>MCAL-32352</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
@@ -14261,31 +14253,31 @@
       </c>
       <c r="Q101" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30813</t>
+          <t>MCAL-32351</t>
         </is>
       </c>
       <c r="R101" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Test Run</t>
         </is>
       </c>
       <c r="S101" s="3" t="inlineStr"/>
       <c r="T101" s="3" t="inlineStr"/>
-      <c r="U101" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U101" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30814</t>
+          <t>MCAL-32352</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
@@ -14360,31 +14352,31 @@
       </c>
       <c r="Q102" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30813</t>
+          <t>MCAL-32351</t>
         </is>
       </c>
       <c r="R102" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Test Run</t>
         </is>
       </c>
       <c r="S102" s="3" t="inlineStr"/>
       <c r="T102" s="3" t="inlineStr"/>
-      <c r="U102" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U102" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30814</t>
+          <t>MCAL-32352</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
@@ -14459,31 +14451,31 @@
       </c>
       <c r="Q103" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30813</t>
+          <t>MCAL-32351</t>
         </is>
       </c>
       <c r="R103" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Test Run</t>
         </is>
       </c>
       <c r="S103" s="3" t="inlineStr"/>
       <c r="T103" s="3" t="inlineStr"/>
-      <c r="U103" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U103" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30814</t>
+          <t>MCAL-32352</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
@@ -14558,31 +14550,31 @@
       </c>
       <c r="Q104" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30813</t>
+          <t>MCAL-32351</t>
         </is>
       </c>
       <c r="R104" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Test Run</t>
         </is>
       </c>
       <c r="S104" s="3" t="inlineStr"/>
       <c r="T104" s="3" t="inlineStr"/>
-      <c r="U104" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U104" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30814</t>
+          <t>MCAL-32352</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
@@ -14657,31 +14649,31 @@
       </c>
       <c r="Q105" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30813</t>
+          <t>MCAL-32351</t>
         </is>
       </c>
       <c r="R105" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Test Run</t>
         </is>
       </c>
       <c r="S105" s="3" t="inlineStr"/>
       <c r="T105" s="3" t="inlineStr"/>
-      <c r="U105" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U105" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30814</t>
+          <t>MCAL-32352</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
@@ -14756,31 +14748,31 @@
       </c>
       <c r="Q106" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30813</t>
+          <t>MCAL-32351</t>
         </is>
       </c>
       <c r="R106" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Test Run</t>
         </is>
       </c>
       <c r="S106" s="3" t="inlineStr"/>
       <c r="T106" s="3" t="inlineStr"/>
-      <c r="U106" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U106" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30814</t>
+          <t>MCAL-32352</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
@@ -14855,31 +14847,31 @@
       </c>
       <c r="Q107" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30813</t>
+          <t>MCAL-32351</t>
         </is>
       </c>
       <c r="R107" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Test Run</t>
         </is>
       </c>
       <c r="S107" s="3" t="inlineStr"/>
       <c r="T107" s="3" t="inlineStr"/>
-      <c r="U107" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U107" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30814</t>
+          <t>MCAL-32352</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
@@ -14954,31 +14946,31 @@
       </c>
       <c r="Q108" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30813</t>
+          <t>MCAL-32351</t>
         </is>
       </c>
       <c r="R108" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Test Run</t>
         </is>
       </c>
       <c r="S108" s="3" t="inlineStr"/>
       <c r="T108" s="3" t="inlineStr"/>
-      <c r="U108" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U108" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30814</t>
+          <t>MCAL-32352</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
@@ -15053,31 +15045,31 @@
       </c>
       <c r="Q109" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30813</t>
+          <t>MCAL-32351</t>
         </is>
       </c>
       <c r="R109" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Test Run</t>
         </is>
       </c>
       <c r="S109" s="3" t="inlineStr"/>
       <c r="T109" s="3" t="inlineStr"/>
-      <c r="U109" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U109" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30814</t>
+          <t>MCAL-32352</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
@@ -15152,31 +15144,31 @@
       </c>
       <c r="Q110" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30813</t>
+          <t>MCAL-32351</t>
         </is>
       </c>
       <c r="R110" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Test Run</t>
         </is>
       </c>
       <c r="S110" s="3" t="inlineStr"/>
       <c r="T110" s="3" t="inlineStr"/>
-      <c r="U110" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U110" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30814</t>
+          <t>MCAL-32352</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
@@ -15251,31 +15243,31 @@
       </c>
       <c r="Q111" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30813</t>
+          <t>MCAL-32351</t>
         </is>
       </c>
       <c r="R111" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Test Run</t>
         </is>
       </c>
       <c r="S111" s="3" t="inlineStr"/>
       <c r="T111" s="3" t="inlineStr"/>
-      <c r="U111" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U111" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30814</t>
+          <t>MCAL-32352</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
@@ -15350,31 +15342,31 @@
       </c>
       <c r="Q112" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30813</t>
+          <t>MCAL-32351</t>
         </is>
       </c>
       <c r="R112" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Test Run</t>
         </is>
       </c>
       <c r="S112" s="3" t="inlineStr"/>
       <c r="T112" s="3" t="inlineStr"/>
-      <c r="U112" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U112" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30814</t>
+          <t>MCAL-32352</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
@@ -15449,31 +15441,31 @@
       </c>
       <c r="Q113" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30813</t>
+          <t>MCAL-32351</t>
         </is>
       </c>
       <c r="R113" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Test Run</t>
         </is>
       </c>
       <c r="S113" s="3" t="inlineStr"/>
       <c r="T113" s="3" t="inlineStr"/>
-      <c r="U113" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U113" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30814</t>
+          <t>MCAL-32352</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Tests</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
@@ -15548,19 +15540,19 @@
       </c>
       <c r="Q114" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30813</t>
+          <t>MCAL-32351</t>
         </is>
       </c>
       <c r="R114" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: GPT- Manual Test Run</t>
+          <t>F29H85xMCAL_01.03.00: GPT - Manual Test Run</t>
         </is>
       </c>
       <c r="S114" s="3" t="inlineStr"/>
       <c r="T114" s="3" t="inlineStr"/>
-      <c r="U114" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U114" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -15614,12 +15606,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>Test Plan</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>Test Plan Key</t>
         </is>
@@ -15641,8 +15633,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="n"/>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="A3" s="11" t="n"/>
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>Test Plan Name</t>
         </is>
@@ -15664,8 +15656,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="n"/>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="A4" s="11" t="n"/>
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>Test Case Key</t>
         </is>
@@ -15687,8 +15679,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="n"/>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="A5" s="11" t="n"/>
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>Test Case Name</t>
         </is>
@@ -15710,8 +15702,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="n"/>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="A6" s="11" t="n"/>
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>Associated Issue(s) Type</t>
         </is>
@@ -15738,8 +15730,8 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="n"/>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="A7" s="11" t="n"/>
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>Associated Issue(s) ID(s)</t>
         </is>
@@ -15761,8 +15753,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="n"/>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="A8" s="11" t="n"/>
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>Test Platform</t>
         </is>
@@ -15784,8 +15776,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="n"/>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="A9" s="11" t="n"/>
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>Test Level</t>
         </is>
@@ -15801,7 +15793,7 @@
 -- "Not Provided" if no 'Test Scope' is provided in Jira</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -15813,8 +15805,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="n"/>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="A10" s="11" t="n"/>
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>Test Description</t>
         </is>
@@ -15836,8 +15828,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="n"/>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="A11" s="11" t="n"/>
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>Test Setup</t>
         </is>
@@ -15859,8 +15851,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="n"/>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="A12" s="11" t="n"/>
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>Pass/Fail Criteria</t>
         </is>
@@ -15882,8 +15874,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="n"/>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="A13" s="11" t="n"/>
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>Test Type</t>
         </is>
@@ -15894,7 +15886,7 @@
 (Map Test Method from Qmetry)</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -15906,15 +15898,15 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="n"/>
-      <c r="B14" s="13" t="n"/>
+      <c r="A14" s="11" t="n"/>
+      <c r="B14" s="12" t="n"/>
       <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Functional:
 Tests covering functional requirements-based  aspects of the software</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -15926,8 +15918,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="n"/>
-      <c r="B15" s="13" t="n"/>
+      <c r="A15" s="11" t="n"/>
+      <c r="B15" s="12" t="n"/>
       <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Compatability:
@@ -15935,7 +15927,7 @@
 ISO/IEC/IEEE 29119-1 Defn: type of testing that measures the degree to which a test item can function satisfactorily alongside other independent products in a shared environment (co-existence), and where necessary, exchanges information with other systems or components (interoperability)</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -15947,15 +15939,15 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="n"/>
-      <c r="B16" s="13" t="n"/>
+      <c r="A16" s="11" t="n"/>
+      <c r="B16" s="12" t="n"/>
       <c r="C16" s="3" t="inlineStr">
         <is>
           <t>Usability:
 Test Case covers usability/api/look and feel aspects of the module including out-of box (OOB) experience</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -15967,15 +15959,15 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="n"/>
-      <c r="B17" s="13" t="n"/>
+      <c r="A17" s="11" t="n"/>
+      <c r="B17" s="12" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Fault Injection:
 Testing based on injection of errors or faults to ensure no unintended consequences</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -15987,8 +15979,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="n"/>
-      <c r="B18" s="13" t="n"/>
+      <c r="A18" s="11" t="n"/>
+      <c r="B18" s="12" t="n"/>
       <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Performance: 
@@ -15996,7 +15988,7 @@
 ISO/IEC/IEEE 29119-1 Defn: type of testing conducted to evaluate the degree to which a test item accomplishes its designated functions within given constraints of time and other resources</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -16008,8 +16000,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="n"/>
-      <c r="B19" s="13" t="n"/>
+      <c r="A19" s="11" t="n"/>
+      <c r="B19" s="12" t="n"/>
       <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Reliability: 
@@ -16017,7 +16009,7 @@
 ISO/IEC/IEEE 29119-1 Defn: type of testing conducted to evaluate the ability of a test item to perform its required functions, including evaluating the frequency with which failures occur, when it is used under stated conditions for a specified period of time</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="D19" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -16029,8 +16021,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="n"/>
-      <c r="B20" s="13" t="n"/>
+      <c r="A20" s="11" t="n"/>
+      <c r="B20" s="12" t="n"/>
       <c r="C20" s="3" t="inlineStr">
         <is>
           <t>Stress:
@@ -16038,7 +16030,7 @@
 ISO/IEC/IEEE 29119-1 Defn: type of performance efficiency testing conducted to evaluate a test item's behaviour under conditions of loading above anticipated or specified capacity requirements, or of resource availability below minimum specified requirements</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="D20" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -16050,8 +16042,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="n"/>
-      <c r="B21" s="13" t="n"/>
+      <c r="A21" s="11" t="n"/>
+      <c r="B21" s="12" t="n"/>
       <c r="C21" s="3" t="inlineStr">
         <is>
           <t>Security:
@@ -16059,7 +16051,7 @@
 ISO/IEC/IEEE 29119-1 Defn: type of testing conducted to evaluate the degree to which a test item, and associated data and information, are protected so that unauthorized persons or systems cannot use, read, or modify them, and authorized persons or systems are not denied access to them</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D21" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -16071,8 +16063,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="n"/>
-      <c r="B22" s="13" t="n"/>
+      <c r="A22" s="11" t="n"/>
+      <c r="B22" s="12" t="n"/>
       <c r="C22" s="3" t="inlineStr">
         <is>
           <t>Maintainability:
@@ -16080,7 +16072,7 @@
 ISO/IEC/IEEE 29119-1 Defn: test type conducted to evaluate the degree of effectiveness and efficiency with which a test item may be modified</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="D22" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -16092,8 +16084,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="n"/>
-      <c r="B23" s="13" t="n"/>
+      <c r="A23" s="11" t="n"/>
+      <c r="B23" s="12" t="n"/>
       <c r="C23" s="3" t="inlineStr">
         <is>
           <t>Portability:
@@ -16101,7 +16093,7 @@
 ISO/IEC/IEEE 29119-1 Defn: type of testing conducted to evaluate the ease with which a test item can be transferred from one hardware or software environment to another, including the level of modification needed for it to be executed in various types of environment</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D23" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -16113,8 +16105,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="n"/>
-      <c r="B24" s="13" t="inlineStr">
+      <c r="A24" s="11" t="n"/>
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>Test Design Technique</t>
         </is>
@@ -16126,7 +16118,7 @@
 (Map Test Derivation Method from Qmetry)</t>
         </is>
       </c>
-      <c r="D24" s="12" t="inlineStr">
+      <c r="D24" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -16138,8 +16130,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="n"/>
-      <c r="B25" s="13" t="n"/>
+      <c r="A25" s="11" t="n"/>
+      <c r="B25" s="12" t="n"/>
       <c r="C25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Requirements-Analysis:
@@ -16147,7 +16139,7 @@
 </t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="D25" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -16159,15 +16151,15 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="n"/>
-      <c r="B26" s="13" t="n"/>
+      <c r="A26" s="11" t="n"/>
+      <c r="B26" s="12" t="n"/>
       <c r="C26" s="3" t="inlineStr">
         <is>
           <t>Boundary Value Analysis:
 Test cases that apply to interfaces and values approaching and crossing the boundaries and out of range values</t>
         </is>
       </c>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="D26" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -16179,15 +16171,15 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="n"/>
-      <c r="B27" s="13" t="n"/>
+      <c r="A27" s="11" t="n"/>
+      <c r="B27" s="12" t="n"/>
       <c r="C27" s="3" t="inlineStr">
         <is>
           <t>Error Guessing:
 Test cases established based on lessons learned and expert judgement to determine situations that may cause software failures or errors to appear</t>
         </is>
       </c>
-      <c r="D27" s="12" t="inlineStr">
+      <c r="D27" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -16199,28 +16191,28 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="12" t="n"/>
-      <c r="B28" s="13" t="n"/>
+      <c r="A28" s="11" t="n"/>
+      <c r="B28" s="12" t="n"/>
       <c r="C28" s="3" t="inlineStr">
         <is>
           <t>Other (Use case analysis; Customer Usage; Requirement analysis; Failure Mode analysis):
 Teams are encouraged to use techniques defined by standards such as ISO/IEC/IEEE 29119-4; which needs to be refelcted within Qmetry</t>
         </is>
       </c>
-      <c r="D28" s="12" t="inlineStr">
+      <c r="D28" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="E28" s="12" t="inlineStr">
+      <c r="E28" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="12" t="n"/>
-      <c r="B29" s="13" t="inlineStr">
+      <c r="A29" s="11" t="n"/>
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t>Test Execution Type</t>
         </is>
@@ -16230,7 +16222,7 @@
           <t>Identifies whether the case is automated or manually or Semi-Automated executed</t>
         </is>
       </c>
-      <c r="D29" s="12" t="inlineStr">
+      <c r="D29" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -16242,8 +16234,8 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="12" t="n"/>
-      <c r="B30" s="13" t="inlineStr">
+      <c r="A30" s="11" t="n"/>
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t>Test Category</t>
         </is>
@@ -16253,7 +16245,7 @@
           <t>Test Categories represent sets of tests that are commonly used.</t>
         </is>
       </c>
-      <c r="D30" s="12" t="inlineStr">
+      <c r="D30" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -16265,15 +16257,15 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="12" t="n"/>
-      <c r="B31" s="13" t="n"/>
+      <c r="A31" s="11" t="n"/>
+      <c r="B31" s="12" t="n"/>
       <c r="C31" s="3" t="inlineStr">
         <is>
           <t>Sanity:
 This Test case is identified to run for Sanity Checks. These are mainly the basic tests that need to be run as part of entry to validate phase</t>
         </is>
       </c>
-      <c r="D31" s="12" t="inlineStr">
+      <c r="D31" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -16285,15 +16277,15 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="12" t="n"/>
-      <c r="B32" s="13" t="n"/>
+      <c r="A32" s="11" t="n"/>
+      <c r="B32" s="12" t="n"/>
       <c r="C32" s="3" t="inlineStr">
         <is>
           <t>Full:
 This category means running all test cases for identified releases</t>
         </is>
       </c>
-      <c r="D32" s="12" t="inlineStr">
+      <c r="D32" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -16305,15 +16297,15 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="12" t="n"/>
-      <c r="B33" s="13" t="n"/>
+      <c r="A33" s="11" t="n"/>
+      <c r="B33" s="12" t="n"/>
       <c r="C33" s="3" t="inlineStr">
         <is>
           <t>Base Regression:
 This Test case is identified to run for the Base Regression / maintenance releases</t>
         </is>
       </c>
-      <c r="D33" s="12" t="inlineStr">
+      <c r="D33" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -16325,8 +16317,8 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="12" t="n"/>
-      <c r="B34" s="13" t="inlineStr">
+      <c r="A34" s="11" t="n"/>
+      <c r="B34" s="12" t="inlineStr">
         <is>
           <t>Test Component(s)</t>
         </is>
@@ -16336,24 +16328,24 @@
           <t xml:space="preserve">The field provides the Component(s) (in Jira) to which the Test Case is mapped to. </t>
         </is>
       </c>
-      <c r="D34" s="12" t="inlineStr">
+      <c r="D34" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="E34" s="12" t="inlineStr">
+      <c r="E34" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="14" t="inlineStr">
+      <c r="A35" s="13" t="inlineStr">
         <is>
           <t>Test Execution</t>
         </is>
       </c>
-      <c r="B35" s="13" t="inlineStr">
+      <c r="B35" s="12" t="inlineStr">
         <is>
           <t>Build/Release Key</t>
         </is>
@@ -16375,8 +16367,8 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="14" t="n"/>
-      <c r="B36" s="13" t="inlineStr">
+      <c r="A36" s="13" t="n"/>
+      <c r="B36" s="12" t="inlineStr">
         <is>
           <t>Defect Key</t>
         </is>
@@ -16398,8 +16390,8 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="14" t="n"/>
-      <c r="B37" s="13" t="inlineStr">
+      <c r="A37" s="13" t="n"/>
+      <c r="B37" s="12" t="inlineStr">
         <is>
           <t>Defect Summary</t>
         </is>
@@ -16421,8 +16413,8 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="14" t="n"/>
-      <c r="B38" s="13" t="inlineStr">
+      <c r="A38" s="13" t="n"/>
+      <c r="B38" s="12" t="inlineStr">
         <is>
           <t>Overall Status</t>
         </is>
@@ -16445,8 +16437,8 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="14" t="n"/>
-      <c r="B39" s="13" t="n"/>
+      <c r="A39" s="13" t="n"/>
+      <c r="B39" s="12" t="n"/>
       <c r="C39" s="3" t="inlineStr">
         <is>
           <t>PASS
@@ -16465,8 +16457,8 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="14" t="n"/>
-      <c r="B40" s="13" t="n"/>
+      <c r="A40" s="13" t="n"/>
+      <c r="B40" s="12" t="n"/>
       <c r="C40" s="3" t="inlineStr">
         <is>
           <t>FAIL
@@ -16485,8 +16477,8 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="14" t="n"/>
-      <c r="B41" s="13" t="n"/>
+      <c r="A41" s="13" t="n"/>
+      <c r="B41" s="12" t="n"/>
       <c r="C41" s="3" t="inlineStr">
         <is>
           <t>BLOCKED
@@ -16505,8 +16497,8 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="14" t="n"/>
-      <c r="B42" s="13" t="n"/>
+      <c r="A42" s="13" t="n"/>
+      <c r="B42" s="12" t="n"/>
       <c r="C42" s="3" t="inlineStr">
         <is>
           <t>WIP
